--- a/test/fixtures/documented.xlsx
+++ b/test/fixtures/documented.xlsx
@@ -441,6 +441,7 @@
       </c>
       <c r="D2">
         <f>B2*C2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -455,6 +456,7 @@
       </c>
       <c r="D3">
         <f>B3*C3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -469,6 +471,7 @@
       </c>
       <c r="D4">
         <f>B4*C4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -483,6 +486,7 @@
       </c>
       <c r="D5">
         <f>B5*C5</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -497,6 +501,7 @@
       </c>
       <c r="D6">
         <f>B6*C6</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -511,6 +516,7 @@
       </c>
       <c r="D7">
         <f>B7*C7</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -525,6 +531,7 @@
       </c>
       <c r="D8">
         <f>B8*C8</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -539,6 +546,7 @@
       </c>
       <c r="D9">
         <f>B9*C9</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -553,6 +561,7 @@
       </c>
       <c r="D10">
         <f>B10*C10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -567,6 +576,7 @@
       </c>
       <c r="D11">
         <f>B11*C11</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -581,6 +591,7 @@
       </c>
       <c r="D12">
         <f>B12*C12</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -595,6 +606,7 @@
       </c>
       <c r="D13">
         <f>B13*C13</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -609,6 +621,7 @@
       </c>
       <c r="D14">
         <f>B14*C14</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -623,6 +636,7 @@
       </c>
       <c r="D15">
         <f>B15*C15</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -637,6 +651,7 @@
       </c>
       <c r="D16">
         <f>B16*C16</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -651,6 +666,7 @@
       </c>
       <c r="D17">
         <f>B17*C17</f>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -665,6 +681,7 @@
       </c>
       <c r="D18">
         <f>B18*C18</f>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -679,6 +696,7 @@
       </c>
       <c r="D19">
         <f>B19*C19</f>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -693,6 +711,7 @@
       </c>
       <c r="D20">
         <f>B20*C20</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -707,6 +726,7 @@
       </c>
       <c r="D21">
         <f>B21*C21</f>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -721,6 +741,7 @@
       </c>
       <c r="D22">
         <f>B22*C22</f>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -735,6 +756,7 @@
       </c>
       <c r="D23">
         <f>B23*C23</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -749,6 +771,7 @@
       </c>
       <c r="D24">
         <f>B24*C24</f>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -763,6 +786,7 @@
       </c>
       <c r="D25">
         <f>B25*C25</f>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -777,6 +801,7 @@
       </c>
       <c r="D26">
         <f>B26*C26</f>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -791,6 +816,7 @@
       </c>
       <c r="D27">
         <f>B27*C27</f>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -805,6 +831,7 @@
       </c>
       <c r="D28">
         <f>B28*C28</f>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -819,6 +846,7 @@
       </c>
       <c r="D29">
         <f>B29*C29</f>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -833,6 +861,7 @@
       </c>
       <c r="D30">
         <f>B30*C30</f>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -847,6 +876,7 @@
       </c>
       <c r="D31">
         <f>B31*C31</f>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -861,6 +891,7 @@
       </c>
       <c r="D32">
         <f>B32*C32</f>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -875,6 +906,7 @@
       </c>
       <c r="D33">
         <f>B33*C33</f>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -889,6 +921,7 @@
       </c>
       <c r="D34">
         <f>B34*C34</f>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -903,6 +936,7 @@
       </c>
       <c r="D35">
         <f>B35*C35</f>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -917,6 +951,7 @@
       </c>
       <c r="D36">
         <f>B36*C36</f>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -931,6 +966,7 @@
       </c>
       <c r="D37">
         <f>B37*C37</f>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -945,6 +981,7 @@
       </c>
       <c r="D38">
         <f>B38*C38</f>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -959,6 +996,7 @@
       </c>
       <c r="D39">
         <f>B39*C39</f>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -973,6 +1011,7 @@
       </c>
       <c r="D40">
         <f>B40*C40</f>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -987,6 +1026,7 @@
       </c>
       <c r="D41">
         <f>B41*C41</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
